--- a/output/pdf_financials_xlsx/GGR.xlsx
+++ b/output/pdf_financials_xlsx/GGR.xlsx
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6.239797</v>
+        <v>-6.239797</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2.189861</v>
+        <v>-2.189861</v>
       </c>
     </row>
     <row r="17">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6.239797</v>
+        <v>-6.239797</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2.189861</v>
+        <v>-2.189861</v>
       </c>
     </row>
     <row r="21">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.239797</v>
+        <v>-6.239797</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2.189861</v>
+        <v>-2.189861</v>
       </c>
     </row>
     <row r="24">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-47.998438</v>
+        <v>47.998438</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-54.746525</v>
+        <v>54.746525</v>
       </c>
     </row>
     <row r="27">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6.239797</v>
+        <v>-6.239797</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.189861</v>
+        <v>-2.189861</v>
       </c>
     </row>
     <row r="28">
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>6.239797</v>
+        <v>-6.239797</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.189861</v>
+        <v>-2.189861</v>
       </c>
     </row>
     <row r="30">
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.014903</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -6849,7 +6849,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>-0.014903</v>
       </c>
@@ -7700,10 +7704,10 @@
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>6.239797</v>
+        <v>-6.239797</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>2.189861</v>
+        <v>-2.189861</v>
       </c>
     </row>
     <row r="95">

--- a/output/pdf_financials_xlsx/GGR.xlsx
+++ b/output/pdf_financials_xlsx/GGR.xlsx
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.079234</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.007506</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.079234</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.007506</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.083687</v>
+        <v>0.004453</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.008623</v>
+        <v>0.001117</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">

--- a/output/pdf_financials_xlsx/GGR.xlsx
+++ b/output/pdf_financials_xlsx/GGR.xlsx
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.023108</v>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.003875</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003021</v>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.02809</v>
+        <v>-0.024215</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.061102</v>
+        <v>0.058081</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
@@ -6150,7 +6150,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -6685,7 +6689,11 @@
           <t>GST Receivable</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>0.003875</v>
       </c>
